--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_quality_issue_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_quality_issue_v2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="质量信息汇总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ods_quality_issue_v2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,200 +413,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="36" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>项目编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>分系统/分任务</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>问题名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>责任科室</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>团队及负责人</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>分管室领导</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>质量问题发生时间</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>质量问题发生周数</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>问题概述</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>原因分类</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>归零计划</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>归零计划是否已在进度信息汇总表中更新</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>新增计划数量</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>归零完成时间</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>归零完成周数</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新时间</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>最后更新周数</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>项目主管</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>填写人</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>project_no</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>subsystem</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>issue_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>dept</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>team_leader</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dept_leader</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>issue_date</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>issue_week</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>issue_summary</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>issue_category</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>zero_plan</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>zero_plan_synced</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>new_plan_count</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>current_progress</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>zero_complete_date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>zero_complete_week</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>last_update_time</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>last_update_week</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>project_manager</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>filled_by</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>控制分系统</t>
+          <t>总体分系统</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>控制器初样软件崩溃问题</t>
+          <t>综合统筹平台综合控制机异常问题</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>控制室</t>
+          <t>总体室</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>陈工团队</t>
+          <t>王工团队</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>赵总</t>
+          <t>张总</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>初样控制软件在持续运行72小时后出现偶发崩溃</t>
+          <t>综合统筹平台接口边界收敛不充分，联调输入条件发生变化</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>软件</t>
+          <t>设计</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>排查内存泄漏并修复；补充回归测试</t>
+          <t>完成综合统筹平台问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -627,24 +596,28 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>归零完成</t>
+          <t>归零完成，已形成技术与管理双闭环</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="Q2" t="n">
-        <v>29</v>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>29</v>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -653,52 +626,54 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>刘工</t>
+          <t>王工</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>结构分系统</t>
+          <t>控制分系统</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>结构件焊缝超差问题</t>
+          <t>飞控执行机构飞控控制器异常问题</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>结构室</t>
+          <t>控制室</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>周工团队</t>
+          <t>陈工团队</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>吴总</t>
+          <t>赵总</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>34</v>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>首件结构件焊缝尺寸超出图纸公差</t>
+          <t>飞控执行机构加工工艺窗口偏窄，首件一致性波动</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -708,7 +683,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>优化焊接工艺参数并返修</t>
+          <t>完成飞控执行机构问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -716,8 +691,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -726,188 +703,212 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>技术已归零等待管理归零评审</t>
+          <t>技术归零完成，等待管理归零确认</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>37</v>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>37</v>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>孙PM</t>
+          <t>陈PM</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>周工</t>
+          <t>陈工</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XM-2025-A01</t>
+          <t>XM-2026-C03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>综合分系统</t>
+          <t>动力分系统</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>联试过程接口异常问题</t>
+          <t>姿轨动力系统动力控制组件异常问题</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>总体室</t>
+          <t>动力室</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>王工团队</t>
+          <t>赵工团队</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>张总</t>
+          <t>孙总</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>45</v>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>控制分系统与结构分系统联试过程中出现电气接口异常</t>
+          <t>姿轨动力系统跨部门接口闭环时序滞后，问题流转不及时</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>设计</t>
+          <t>管理</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>重新设计接口并更新图纸</t>
+          <t>完成姿轨动力系统问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>未完成归零</t>
+          <t>已完成管理归零</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>接口方案设计中</t>
+          <t>管理归零已完成，技术验证收口中</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>51</v>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>孙PM</t>
+          <t>赵PM</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>王工</t>
+          <t>赵工</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>制导分系统</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>热试车异常振动问题</t>
+          <t>惯导制导系统制导计算机异常问题</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>制导室</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>赵工团队</t>
+          <t>林工团队</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>马总</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>47</v>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>热试车过程中发动机出现异常振动峰值</t>
+          <t>惯导制导系统关键器件批次一致性不足，筛选后仍存在漂移</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>设计</t>
+          <t>元器件</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>排查振动根因；设计迭代优化</t>
+          <t>完成惯导制导系统问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -916,80 +917,86 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>技术归零进行中，已完成仿真复现</t>
-        </is>
-      </c>
+          <t>问题定位与归零措施执行中</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>52</v>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>林PM</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>赵工</t>
+          <t>林工</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>XM-2025-A02</t>
+          <t>XM-2026-C05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>动力分系统</t>
+          <t>软件分系统</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>喷管型面加工缺陷</t>
+          <t>实时软件平台实时软件构件异常问题</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>动力室</t>
+          <t>软件室</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>钱工团队</t>
+          <t>沈工团队</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>孙总</t>
+          <t>胡总</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>28</v>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>喷管内型面加工后出现局部缺陷</t>
+          <t>实时软件平台试验操作顺序不规范，引入重复性异常</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>工艺</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>工艺改进并重新加工</t>
+          <t>完成实时软件平台问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,8 +1004,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1007,88 +1016,94 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>归零完成</t>
+          <t>归零完成，已形成技术与管理双闭环</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>34</v>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>34</v>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>赵PM</t>
+          <t>沈PM</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>钱工</t>
+          <t>沈工</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>结构分系统</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>仿真数据偏差问题</t>
+          <t>复合结构组件主承力舱段异常问题</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>结构室</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>林工团队</t>
+          <t>周工团队</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>吴总</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>21</v>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>仿真结果与理论计算值存在3%偏差</t>
+          <t>复合结构组件外协件返修周期超预期，影响到货节奏</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>设计</t>
+          <t>外协</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>重新核对算法参数并修正</t>
+          <t>完成复合结构组件问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1096,8 +1111,10 @@
           <t>是</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1106,141 +1123,161 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>技术已归零</t>
+          <t>技术归零完成，等待管理归零确认</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>26</v>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>26</v>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>林PM</t>
+          <t>周PM</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>林工</t>
+          <t>周工</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XM-2026-B01</t>
+          <t>XM-2026-C07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>制导分系统</t>
+          <t>电源分系统</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>硬件板卡元器件失效</t>
+          <t>高可靠电源系统电源管理单元异常问题</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>制导室</t>
+          <t>电源室</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>黄工团队</t>
+          <t>宋工团队</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>马总</t>
+          <t>高总</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>35</v>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>初样硬件板卡电容元器件批次失效</t>
+          <t>高可靠电源系统实时任务调度冲突，长稳运行存在异常</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>元器件</t>
+          <t>软件</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>更换合格批次元器件；补充筛选试验</t>
+          <t>完成高可靠电源系统问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>2</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>未完成归零</t>
+          <t>已完成管理归零</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>归零计划进行中</t>
+          <t>管理归零已完成，技术验证收口中</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>38</v>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>林PM</t>
+          <t>宋PM</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>黄工</t>
+          <t>宋工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>电子分系统</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>天线方向图偏离问题</t>
+          <t>电子载荷组件载荷处理模块异常问题</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1260,60 +1297,56 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>19</v>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>遥测天线方向图偏离仿真预期</t>
+          <t>电子载荷组件高低温应力下性能裕度下降，边界条件暴露</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>调整天线结构参数</t>
-        </is>
-      </c>
+          <t>环境</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>已完成技术和管理归零</t>
+          <t>未完成归零</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>归零完成</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>22</v>
-      </c>
+          <t>问题定位与归零措施执行中</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>22</v>
+          <t>2026-11-27</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1329,136 +1362,154 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>XM-2026-B02</t>
+          <t>XM-2026-C09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>遥测分系统</t>
+          <t>测控分系统</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>遥控软件协议不兼容</t>
+          <t>测控链路系统测控主机异常问题</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>软件室</t>
+          <t>测控室</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>郭工团队</t>
+          <t>田工团队</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>朱总</t>
+          <t>潘总</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>36</v>
+          <t>2026-12-07</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>遥控软件与新版测控协议不完全兼容</t>
+          <t>测控链路系统现场条件变化引起的综合性异常待进一步定位</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>软件</t>
+          <t>其他</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>协议适配层重构</t>
+          <t>完成测控链路系统问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>未完成归零</t>
+          <t>已完成技术和管理归零</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>协议分析中</t>
+          <t>归零完成，已形成技术与管理双闭环</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v>40</v>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>徐PM</t>
+          <t>田PM</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>郭工</t>
+          <t>田工</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XM-2026-B03</t>
+          <t>XM-2026-C10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>电源分系统</t>
+          <t>试验分系统</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>蓄电池组循环性能不足</t>
+          <t>环境试验保障平台综合试验工装异常问题</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>电源室</t>
+          <t>试验室</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>宋工团队</t>
+          <t>柳工团队</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>高总</t>
+          <t>曹总</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>26</v>
+          <t>2027-01-06</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>蓄电池组循环寿命测试未达指标</t>
+          <t>环境试验保障平台接口边界收敛不充分，联调输入条件发生变化</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1468,16 +1519,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>优化电池管理策略</t>
+          <t>完成环境试验保障平台问题归零并输出验证记录</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1486,502 +1539,35 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>技术已归零</t>
+          <t>技术归零完成，等待管理归零确认</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>33</v>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>33</v>
+          <t>2027-02-03</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>宋PM</t>
+          <t>柳PM</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
-        <is>
-          <t>宋工</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>XM-2026-B04</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>结构分系统</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>主承力结构仿真应力集中</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>结构室</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>邓工团队</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>吴总</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>仿真发现局部应力集中超限</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>增加加强筋并重新仿真</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>已完成技术和管理归零</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>归零完成</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>25</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>邓PM</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>邓工</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>XM-2026-B05</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>测控分系统</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>测控主机元器件到货批次问题</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>测控室</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>田工团队</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>潘总</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>20</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>关键元器件到货批次存在一致性问题</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>元器件</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>更换备选方案元器件</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>已完成技术和管理归零</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>归零完成</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>26</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>26</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>田PM</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>田工</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>XM-2026-B05</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>测控分系统</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>测控软件接口协议缺陷</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>软件室</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>姜工团队</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>朱总</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>28</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>测控软件与地面站协议解析存在缺陷</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>软件</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>协议解析模块重构</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>未完成归零</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>归零计划编制中</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="S14" t="n">
-        <v>32</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>田PM</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>姜工</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>XM-2026-B06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>综合试验分系统</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EMC试验超标问题</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>试验室</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>柳工团队</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>曹总</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>37</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>电磁兼容试验中部分频段超标</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>屏蔽与滤波优化</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>未完成归零</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>设计优化进行中</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>40</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>柳PM</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>柳工</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>XM-2026-B06</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>综合试验分系统</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>可靠性试验失效问题</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>试验室</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>柳工团队</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>曹总</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>48</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>可靠性试验中发现局部失效</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>设计</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>失效分析与设计改进</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>未完成归零</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>失效分析进行中，拟召开技术归零评审</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-12-14</t>
-        </is>
-      </c>
-      <c r="S16" t="n">
-        <v>51</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>柳PM</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
         <is>
           <t>柳工</t>
         </is>
